--- a/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62214</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71254</t>
+          <t>72758</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107740</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114725</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158451</t>
+          <t>159213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969509</t>
+          <t>971513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>997505</t>
+          <t>998202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1207373</t>
+          <t>1204863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1243859</t>
+          <t>1242355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2188384</t>
+          <t>2187622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2232110</t>
+          <t>2233913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45548</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73763</t>
+          <t>76368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109460</t>
+          <t>109541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1647865</t>
+          <t>1647904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1670426</t>
+          <t>1670578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1513910</t>
+          <t>1511305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1543584</t>
+          <t>1542616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3171626</t>
+          <t>3171545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3207835</t>
+          <t>3209069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528864</t>
+          <t>531435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543338</t>
+          <t>544444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462233</t>
+          <t>461936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473375</t>
+          <t>473335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997752</t>
+          <t>997921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015299</t>
+          <t>1015202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129417</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181201</t>
+          <t>182661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216538</t>
+          <t>217358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>278899</t>
+          <t>277457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3165223</t>
+          <t>3165544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3203898</t>
+          <t>3202917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3197996</t>
+          <t>3196536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3249780</t>
+          <t>3246502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6376842</t>
+          <t>6378284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6439203</t>
+          <t>6438383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>31248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61553</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82985</t>
+          <t>84232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123534</t>
+          <t>120861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122684</t>
+          <t>123225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169232</t>
+          <t>170548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>913090</t>
+          <t>914516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>942487</t>
+          <t>943395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1214263</t>
+          <t>1216936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1254812</t>
+          <t>1253565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2143208</t>
+          <t>2141892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2189756</t>
+          <t>2189215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>42536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>74352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>83618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122339</t>
+          <t>123242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1904117</t>
+          <t>1906525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1932914</t>
+          <t>1932982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1682272</t>
+          <t>1683451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1713276</t>
+          <t>1715267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3599421</t>
+          <t>3598518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3640522</t>
+          <t>3638142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22154</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48184</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452219</t>
+          <t>453699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470427</t>
+          <t>471439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434550</t>
+          <t>434666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>451341</t>
+          <t>450794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891629</t>
+          <t>892983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>917659</t>
+          <t>918073</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83723</t>
+          <t>85410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>128325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150708</t>
+          <t>150335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202115</t>
+          <t>203274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244741</t>
+          <t>248123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313242</t>
+          <t>315135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3291717</t>
+          <t>3291457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3336059</t>
+          <t>3334372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3352115</t>
+          <t>3350956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3403522</t>
+          <t>3403895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6660770</t>
+          <t>6658877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6729271</t>
+          <t>6725889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74493</t>
+          <t>74558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159845</t>
+          <t>159728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211913</t>
+          <t>213138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214114</t>
+          <t>214867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>271661</t>
+          <t>277446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679854</t>
+          <t>679789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>708665</t>
+          <t>710268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>782747</t>
+          <t>781522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>834815</t>
+          <t>834932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1477346</t>
+          <t>1471561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1534893</t>
+          <t>1534140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61495</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98243</t>
+          <t>97092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156035</t>
+          <t>152934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207786</t>
+          <t>206190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226116</t>
+          <t>224129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>291085</t>
+          <t>288036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1978142</t>
+          <t>1979293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2014890</t>
+          <t>2013861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1780514</t>
+          <t>1782110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1832265</t>
+          <t>1835366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3773600</t>
+          <t>3776649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3838569</t>
+          <t>3840556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>27058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35891</t>
+          <t>37210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519751</t>
+          <t>519828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537936</t>
+          <t>537368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513249</t>
+          <t>511930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>534177</t>
+          <t>533153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1039370</t>
+          <t>1040043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1067750</t>
+          <t>1066948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131129</t>
+          <t>132583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177404</t>
+          <t>179043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>351646</t>
+          <t>351364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>427379</t>
+          <t>429350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>499749</t>
+          <t>496942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>589795</t>
+          <t>591848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3200214</t>
+          <t>3198575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3246489</t>
+          <t>3245035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3104721</t>
+          <t>3102750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3180454</t>
+          <t>3180736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6319923</t>
+          <t>6317870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6409969</t>
+          <t>6412776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>36167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46695</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67934</t>
+          <t>70296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68359</t>
+          <t>69611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>96770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480202</t>
+          <t>478771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498073</t>
+          <t>498171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687574</t>
+          <t>685212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>708813</t>
+          <t>708091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1173956</t>
+          <t>1173676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1202087</t>
+          <t>1200835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46999</t>
+          <t>47571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92004</t>
+          <t>94103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87244</t>
+          <t>85530</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>836127</t>
+          <t>768522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149724</t>
+          <t>148606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1069555</t>
+          <t>1031290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2198323</t>
+          <t>2196224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2243328</t>
+          <t>2242756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1401696</t>
+          <t>1469301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2150579</t>
+          <t>2152293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3458595</t>
+          <t>3496860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4378426</t>
+          <t>4379544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>48900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617855</t>
+          <t>617760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636354</t>
+          <t>636492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631952</t>
+          <t>633887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648796</t>
+          <t>648737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258800</t>
+          <t>1258186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282177</t>
+          <t>1281398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84800</t>
+          <t>85883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139246</t>
+          <t>136606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161898</t>
+          <t>161224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>988686</t>
+          <t>975108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262695</t>
+          <t>264233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1186078</t>
+          <t>1204134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3312643</t>
+          <t>3315283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3367089</t>
+          <t>3366006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2665108</t>
+          <t>2678686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3491896</t>
+          <t>3492570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5919605</t>
+          <t>5901549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6842988</t>
+          <t>6841450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>34431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60210</t>
+          <t>60220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72758</t>
+          <t>73494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>109522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112922</t>
+          <t>113710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>971513</t>
+          <t>971503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>998202</t>
+          <t>997292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1204863</t>
+          <t>1205591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1242355</t>
+          <t>1241619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2187622</t>
+          <t>2188598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2233913</t>
+          <t>2233125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76368</t>
+          <t>73436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72017</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109541</t>
+          <t>111662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1647904</t>
+          <t>1648688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1670578</t>
+          <t>1670404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1511305</t>
+          <t>1514237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1542616</t>
+          <t>1543590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3171545</t>
+          <t>3169424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3209069</t>
+          <t>3208786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531435</t>
+          <t>530130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544444</t>
+          <t>543845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461936</t>
+          <t>462064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473335</t>
+          <t>473364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997921</t>
+          <t>997754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015202</t>
+          <t>1015594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73626</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110999</t>
+          <t>109749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132695</t>
+          <t>129995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>181669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217358</t>
+          <t>215957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277457</t>
+          <t>278037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3165544</t>
+          <t>3166794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3202917</t>
+          <t>3202364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3196536</t>
+          <t>3197528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3246502</t>
+          <t>3249202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6378284</t>
+          <t>6377704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6438383</t>
+          <t>6439784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31248</t>
+          <t>31575</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60127</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84232</t>
+          <t>84075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120861</t>
+          <t>123607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123225</t>
+          <t>125337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170548</t>
+          <t>170393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>914516</t>
+          <t>913463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>943395</t>
+          <t>943068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1216936</t>
+          <t>1214190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1253565</t>
+          <t>1253722</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2141892</t>
+          <t>2142047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2189215</t>
+          <t>2187103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>31259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>57783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42536</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74352</t>
+          <t>74315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83618</t>
+          <t>84137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123242</t>
+          <t>122325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1906525</t>
+          <t>1906174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1932982</t>
+          <t>1932698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1683451</t>
+          <t>1683488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1715267</t>
+          <t>1713624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3598518</t>
+          <t>3599435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3638142</t>
+          <t>3637623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27482</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453699</t>
+          <t>454063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471439</t>
+          <t>471181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434666</t>
+          <t>435318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450794</t>
+          <t>451531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>892983</t>
+          <t>892783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>918073</t>
+          <t>917682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85410</t>
+          <t>83585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128325</t>
+          <t>126994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150335</t>
+          <t>150299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203274</t>
+          <t>202908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248123</t>
+          <t>246398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315135</t>
+          <t>314170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3291457</t>
+          <t>3292788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3334372</t>
+          <t>3336197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3350956</t>
+          <t>3351322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3403895</t>
+          <t>3403931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6658877</t>
+          <t>6659842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6725889</t>
+          <t>6727614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44079</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74558</t>
+          <t>74723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159728</t>
+          <t>160284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213138</t>
+          <t>210834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214867</t>
+          <t>213869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277446</t>
+          <t>274357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679789</t>
+          <t>679624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>710268</t>
+          <t>708390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>781522</t>
+          <t>783826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>834932</t>
+          <t>834376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1471561</t>
+          <t>1474650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1534140</t>
+          <t>1535138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97092</t>
+          <t>97118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152934</t>
+          <t>153775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206190</t>
+          <t>207385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224129</t>
+          <t>228406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288036</t>
+          <t>291911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1979293</t>
+          <t>1979267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2013861</t>
+          <t>2014051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1782110</t>
+          <t>1780915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1835366</t>
+          <t>1834525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3776649</t>
+          <t>3772774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3840556</t>
+          <t>3836279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27058</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55984</t>
+          <t>55565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519828</t>
+          <t>518732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537368</t>
+          <t>537025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511930</t>
+          <t>513120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533153</t>
+          <t>533724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1040043</t>
+          <t>1040462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1066948</t>
+          <t>1066457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132583</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179043</t>
+          <t>179584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>351364</t>
+          <t>349970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>429350</t>
+          <t>428311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>496942</t>
+          <t>495159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>591848</t>
+          <t>587691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3198575</t>
+          <t>3198034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3245035</t>
+          <t>3249415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3102750</t>
+          <t>3103789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3180736</t>
+          <t>3182130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6317870</t>
+          <t>6322027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6412776</t>
+          <t>6414559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>19876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>62931</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>52217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70296</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>82092</t>
+          <t>91590</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>78517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96770</t>
+          <t>108760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>490091</t>
+          <t>549869</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478771</t>
+          <t>537301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498171</t>
+          <t>558653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>698263</t>
+          <t>759107</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685212</t>
+          <t>746162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>708091</t>
+          <t>769821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1188354</t>
+          <t>1308977</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1173676</t>
+          <t>1291807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1200835</t>
+          <t>1322050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69751</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94103</t>
+          <t>94932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>287907</t>
+          <t>95534</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85530</t>
+          <t>79675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>768522</t>
+          <t>114598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,22 +5950,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>357658</t>
+          <t>169295</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148606</t>
+          <t>144467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1031290</t>
+          <t>198303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2220576</t>
+          <t>2156804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2196224</t>
+          <t>2135634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2242756</t>
+          <t>2173928</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1949916</t>
+          <t>2075858</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1469301</t>
+          <t>2056794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2152293</t>
+          <t>2091717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,27 +6063,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4170492</t>
+          <t>4232664</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3496860</t>
+          <t>4203656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4379544</t>
+          <t>4257492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28863</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35220</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25688</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>54019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>629377</t>
+          <t>693290</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617760</t>
+          <t>682671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636492</t>
+          <t>700886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>642488</t>
+          <t>714282</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633887</t>
+          <t>704781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648737</t>
+          <t>721377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1271866</t>
+          <t>1407572</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258186</t>
+          <t>1392445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1281398</t>
+          <t>1417821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>111843</t>
+          <t>120719</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85883</t>
+          <t>100953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136606</t>
+          <t>147433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>363127</t>
+          <t>179059</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161224</t>
+          <t>156784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>975108</t>
+          <t>204166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>474971</t>
+          <t>299778</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264233</t>
+          <t>270649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1204134</t>
+          <t>335163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3340046</t>
+          <t>3399964</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3315283</t>
+          <t>3373250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366006</t>
+          <t>3419730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3290667</t>
+          <t>3549248</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2678686</t>
+          <t>3524141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3492570</t>
+          <t>3571523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6630712</t>
+          <t>6949212</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5901549</t>
+          <t>6913827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6841450</t>
+          <t>6978341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
